--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486674_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486674_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. SOTO MADRIGAL</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6074</v>
+        <v>1.757</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4334</v>
+        <v>3.5718</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.826</v>
+        <v>-1.8148</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1259</v>
+        <v>1.2231</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6277</v>
+        <v>-1.076</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5018</v>
+        <v>2.2991</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3858</v>
+        <v>3.2451</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9593</v>
+        <v>-0.6614</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4265</v>
+        <v>3.9065</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.5117</v>
+        <v>-2.022</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.587</v>
+        <v>-0.4146</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9247</v>
+        <v>-1.6074</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.1931</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2466</v>
+        <v>-0.1379</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2407</v>
+        <v>0.2341</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0059</v>
+        <v>-0.372</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2856</v>
+        <v>0.2856</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>D. SOTO MADRIGAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4756</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3649</v>
+        <v>2.7094</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8893</v>
+        <v>-1.9005</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2231</v>
+        <v>-0.1259</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.076</v>
+        <v>-0.6277</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2991</v>
+        <v>0.5018</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2451</v>
+        <v>2.3858</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6614</v>
+        <v>0.9593</v>
       </c>
       <c r="L3" t="n">
-        <v>3.9065</v>
+        <v>1.4265</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.022</v>
+        <v>-2.5117</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4146</v>
+        <v>-1.587</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6074</v>
+        <v>-0.9247</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.1931</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4192</v>
+        <v>0.4481</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0273</v>
+        <v>0.5168</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4465</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2856</v>
+        <v>-0.2856</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5177</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>1.1028</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5851</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.5784</v>
@@ -766,13 +766,13 @@
         <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2538</v>
+        <v>-0.1793</v>
       </c>
       <c r="T4" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.033</v>
+        <v>0.0414</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.114</v>
+        <v>-0.5728</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0838</v>
+        <v>0.6701</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9698</v>
+        <v>-1.243</v>
       </c>
       <c r="G5" t="n">
         <v>-2.2421</v>
@@ -844,13 +844,13 @@
         <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.593</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0558</v>
+        <v>-0.4695</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1496</v>
+        <v>-0.1236</v>
       </c>
       <c r="V5" t="n">
         <v>2.4554</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.473</v>
+        <v>-1.2755</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8088</v>
+        <v>-1.6362</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3359</v>
+        <v>0.3607</v>
       </c>
       <c r="G6" t="n">
         <v>0.0776</v>
@@ -922,13 +922,13 @@
         <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4301</v>
+        <v>-0.3724</v>
       </c>
       <c r="T6" t="n">
-        <v>0.772</v>
+        <v>-0.0554</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3418</v>
+        <v>-0.317</v>
       </c>
       <c r="V6" t="n">
         <v>0.3709</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.017</v>
+        <v>-1.3675</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8667</v>
+        <v>-0.1428</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1502</v>
+        <v>-1.2247</v>
       </c>
       <c r="G7" t="n">
         <v>0.7026</v>
@@ -1000,13 +1000,13 @@
         <v>1.9308</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0978</v>
+        <v>-0.4483</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1036</v>
+        <v>-0.3797</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0059</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6565</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.5821</v>
+        <v>-4.3504</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9903</v>
+        <v>-0.7835</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.5918</v>
+        <v>-3.567</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6538</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7006</v>
+        <v>-0.4689</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.359</v>
+        <v>-0.1521</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3416</v>
+        <v>-0.3168</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. SIBENIK</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.0048</v>
+        <v>-5.3599</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6271</v>
+        <v>-3.4066</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3777</v>
+        <v>-1.9533</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.38</v>
+        <v>-4.5599</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3387</v>
+        <v>-0.3732</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0413</v>
+        <v>-4.1866</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5029</v>
+        <v>-1.3787</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1308</v>
+        <v>0.8004</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3721</v>
+        <v>-2.1791</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8771</v>
+        <v>-3.1811</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.2079</v>
+        <v>-1.1736</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6692</v>
+        <v>-2.0075</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>-1.1585</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2041</v>
+        <v>-1.1861</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1934</v>
+        <v>-0.8694</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0107</v>
+        <v>-0.3168</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>L. SIBENIK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3032</v>
+        <v>-5.8973</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0271</v>
+        <v>-3.4203</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2761</v>
+        <v>-2.4771</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.5599</v>
+        <v>-4.38</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3732</v>
+        <v>-2.3387</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.1866</v>
+        <v>-2.0413</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3787</v>
+        <v>-1.5029</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8004</v>
+        <v>-0.1308</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1791</v>
+        <v>-1.3721</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1811</v>
+        <v>-2.8771</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1736</v>
+        <v>-2.2079</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0075</v>
+        <v>-0.6692</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3862</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1585</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1295</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4899</v>
+        <v>0.0134</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.6654</v>
+        <v>-15.6652</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3351</v>
+        <v>-1.3353</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.3301</v>
+        <v>-14.3303</v>
       </c>
       <c r="G11" t="n">
         <v>-11.38</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.864</v>
+        <v>-5.863999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>-5.5159</v>
@@ -1303,7 +1303,7 @@
         <v>-10.6934</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9652999999999997</v>
+        <v>-0.9652999999999998</v>
       </c>
       <c r="Q11" t="n">
         <v>-11.5849</v>
@@ -1312,13 +1312,13 @@
         <v>10.6193</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.0345</v>
+        <v>-3.0344</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3824</v>
+        <v>-1.3825</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6518</v>
+        <v>-1.652</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2856000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4261</v>
+        <v>5.0165</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6865</v>
+        <v>5.3762</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2604</v>
+        <v>-0.3597</v>
       </c>
       <c r="G12" t="n">
         <v>5.0453</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>0.651</v>
+        <v>0.2414</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0273</v>
+        <v>-0.283</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6237</v>
+        <v>0.5244</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6565</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2552</v>
+        <v>3.8277</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2478</v>
+        <v>2.9215</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0074</v>
+        <v>0.9062</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3851</v>
+        <v>1.6307</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1177</v>
+        <v>0.8689</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2674</v>
+        <v>0.7618</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9725</v>
+        <v>2.8254</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3252</v>
+        <v>1.5593</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6473</v>
+        <v>1.266</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5874</v>
+        <v>-1.1946</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2075</v>
+        <v>-0.6904</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3799</v>
+        <v>-0.5042</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1585</v>
+        <v>1.9308</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8701</v>
+        <v>0.7449</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4338</v>
+        <v>0.2892</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4363</v>
+        <v>0.4557</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0926</v>
+        <v>3.3574</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7146</v>
+        <v>2.5239</v>
       </c>
       <c r="F14" t="n">
-        <v>1.378</v>
+        <v>0.8335</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6307</v>
+        <v>2.3851</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8689</v>
+        <v>0.1177</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7618</v>
+        <v>2.2674</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8254</v>
+        <v>2.9725</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5593</v>
+        <v>0.3252</v>
       </c>
       <c r="L14" t="n">
-        <v>1.266</v>
+        <v>2.6473</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1946</v>
+        <v>-0.5874</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6904</v>
+        <v>-0.2075</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5042</v>
+        <v>-0.3799</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9308</v>
+        <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0098</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0824</v>
+        <v>0.7098</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9275</v>
+        <v>0.2625</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4689</v>
+        <v>2.6553</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9668</v>
+        <v>3.6565</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4979</v>
+        <v>-1.0012</v>
       </c>
       <c r="G15" t="n">
         <v>2.4692</v>
@@ -1624,13 +1624,13 @@
         <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1933</v>
+        <v>-0.0069</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7167</v>
+        <v>0.4064</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.91</v>
+        <v>-0.4133</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4177</v>
+        <v>2.6205</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7522</v>
+        <v>3.8557</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3345</v>
+        <v>-1.2352</v>
       </c>
       <c r="G16" t="n">
         <v>2.7653</v>
@@ -1702,13 +1702,13 @@
         <v>0.7723</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1545</v>
+        <v>0.0482</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3307</v>
+        <v>0.4342</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4852</v>
+        <v>-0.3859</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6681</v>
+        <v>0.8749</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0835</v>
+        <v>0.1234</v>
       </c>
       <c r="F17" t="n">
         <v>0.7514999999999999</v>
@@ -1780,10 +1780,10 @@
         <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1104</v>
+        <v>0.3172</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1655</v>
+        <v>0.0413</v>
       </c>
       <c r="U17" t="n">
         <v>0.2759</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GUERRA LOZANO</t>
+          <t>A. CHACON GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0525</v>
+        <v>0.3029</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2955</v>
+        <v>-0.5114</v>
       </c>
       <c r="F18" t="n">
-        <v>1.243</v>
+        <v>0.8143</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4306</v>
+        <v>-0.5535</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1654</v>
+        <v>0.0343</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.596</v>
+        <v>-0.5878</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2256</v>
+        <v>0.53</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4418</v>
+        <v>1.1381</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2162</v>
+        <v>-0.6081</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6563</v>
+        <v>-1.0835</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2764</v>
+        <v>-1.1038</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3799</v>
+        <v>0.0203</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5446</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0892</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0548</v>
+        <v>-0.076</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6403</v>
+        <v>0.276</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2277</v>
+        <v>0.6565</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CHACON GARCIA</t>
+          <t>G. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2557</v>
+        <v>-0.2304</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8217</v>
+        <v>-1.3989</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5659999999999999</v>
+        <v>1.1685</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5535</v>
+        <v>-0.4306</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0343</v>
+        <v>1.1654</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5878</v>
+        <v>-1.596</v>
       </c>
       <c r="J19" t="n">
-        <v>0.53</v>
+        <v>0.2256</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1381</v>
+        <v>1.4418</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6081</v>
+        <v>-1.2162</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0835</v>
+        <v>-0.6563</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1038</v>
+        <v>-0.2764</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0203</v>
+        <v>-0.3799</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>-3.0892</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3586</v>
+        <v>0.5172</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3863</v>
+        <v>-0.0486</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0277</v>
+        <v>0.5658</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5617</v>
+        <v>-0.9827</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3786</v>
+        <v>-1.5512</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8169</v>
+        <v>0.5685</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5097</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.11</v>
+        <v>0.469</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4968</v>
+        <v>0.3306</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3867</v>
+        <v>0.1384</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9421</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7934</v>
+        <v>-1.7767</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4585</v>
+        <v>-0.6653</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3349</v>
+        <v>-1.1114</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7865</v>
@@ -2092,13 +2092,13 @@
         <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4855</v>
+        <v>-0.4689</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0548</v>
+        <v>-0.152</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5404</v>
+        <v>-0.3169</v>
       </c>
       <c r="V21" t="n">
         <v>0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>15.6653</v>
+        <v>15.6654</v>
       </c>
       <c r="E22" t="n">
-        <v>14.3301</v>
+        <v>14.3304</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3351</v>
+        <v>1.335</v>
       </c>
       <c r="G22" t="n">
         <v>11.3799</v>
@@ -2161,7 +2161,7 @@
         <v>-5.1775</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9655000000000002</v>
+        <v>0.9654999999999998</v>
       </c>
       <c r="Q22" t="n">
         <v>-10.6194</v>
@@ -2170,13 +2170,13 @@
         <v>11.5847</v>
       </c>
       <c r="S22" t="n">
-        <v>3.0345</v>
+        <v>3.0344</v>
       </c>
       <c r="T22" t="n">
         <v>1.6519</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3825</v>
+        <v>1.3826</v>
       </c>
       <c r="V22" t="n">
         <v>0.2855999999999999</v>
